--- a/rcads/data/xls/90_Languages.xlsx
+++ b/rcads/data/xls/90_Languages.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_90_Languages"/>
   </sheets>
   <definedNames>
-    <definedName name="_90_Languages">'_90_Languages'!$A$1:$H$41</definedName>
+    <definedName name="_90_Languages">'_90_Languages'!$A$1:$H$42</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -1493,6 +1493,31 @@
         </is>
       </c>
     </row>
+    <row outlineLevel="0" r="42">
+      <c r="A42" s="0">
+        <v>41</v>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>Zulu</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>ZU</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>ZUL</t>
+        </is>
+      </c>
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t>isiZulu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
